--- a/laboratory_forms/023_university_laboratory_equipment_inspection_form--laboratory_forms.xlsx
+++ b/laboratory_forms/023_university_laboratory_equipment_inspection_form--laboratory_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1534,17 +1534,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>equipment_status_choices</t>
+          <t>maintenance_frequency_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>maintenance_required</t>
+          <t>every_1_day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maintenance Required</t>
+          <t>Every 1 day</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>every_1_day</t>
+          <t>every_1_week</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Every 1 day</t>
+          <t>Every 1 week</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>every_1_week</t>
+          <t>every_1_month</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Every 1 week</t>
+          <t>Every 1 month</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>every_1_month</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Every 1 month</t>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
@@ -1607,27 +1607,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>every_6_months</t>
+          <t>every_1_year</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Every 6 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>maintenance_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>every_1_year</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Every 1 year</t>
         </is>
